--- a/Files/Madden26/IE/Season2/FreeAgency/Input/PositionNeeds.xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Input/PositionNeeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenTools/Files/Madden26/IE/Season2/FreeAgency/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{7C439BFB-0DBF-4097-AD0B-C529E75DCE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65F48151-89F3-4A95-9BA0-86B7988BAF03}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{7C439BFB-0DBF-4097-AD0B-C529E75DCE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B585557-95F8-415E-91CA-F1BE1B3039E8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DE15C3C6-B90C-4AA8-AF55-EC28F49C3043}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE15C3C6-B90C-4AA8-AF55-EC28F49C3043}"/>
   </bookViews>
   <sheets>
     <sheet name="TierNeedLogic" sheetId="1" r:id="rId1"/>
@@ -328,10 +328,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,19 +648,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6437B3-F8C6-4C30-BAA1-BB8B4D93E54D}">
   <dimension ref="A1:H86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -690,7 +686,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -716,7 +712,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -742,7 +738,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -768,7 +764,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -794,7 +790,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -820,7 +816,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -846,7 +842,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -872,7 +868,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -898,7 +894,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -924,7 +920,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -950,7 +946,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -976,7 +972,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1002,7 +998,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1028,7 +1024,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -1054,7 +1050,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -1080,7 +1076,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -1106,7 +1102,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1132,7 +1128,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1149,16 +1145,16 @@
         <v>70</v>
       </c>
       <c r="F19">
+        <v>74</v>
+      </c>
+      <c r="G19">
         <v>75</v>
-      </c>
-      <c r="G19">
-        <v>74</v>
       </c>
       <c r="H19">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1184,7 +1180,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1210,7 +1206,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1236,7 +1232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1262,7 +1258,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1288,7 +1284,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1314,7 +1310,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1340,7 +1336,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1362,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1392,7 +1388,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1418,7 +1414,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1444,7 +1440,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1470,7 +1466,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1496,7 +1492,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1518,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1548,7 +1544,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1574,7 +1570,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1600,7 +1596,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1626,7 +1622,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1652,7 +1648,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -1678,7 +1674,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1700,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1730,7 +1726,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -1756,7 +1752,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1782,7 +1778,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -1808,7 +1804,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -1834,7 +1830,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -1860,7 +1856,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -1886,7 +1882,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -1912,7 +1908,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -1938,7 +1934,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -1964,7 +1960,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -1990,7 +1986,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -2016,7 +2012,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -2042,7 +2038,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -2068,7 +2064,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2094,7 +2090,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -2120,7 +2116,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -2146,7 +2142,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -2172,7 +2168,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -2198,7 +2194,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2224,7 +2220,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -2250,7 +2246,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -2276,7 +2272,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -2302,7 +2298,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -2328,7 +2324,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -2354,7 +2350,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -2380,7 +2376,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -2406,7 +2402,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -2432,7 +2428,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -2458,7 +2454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -2484,7 +2480,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -2510,7 +2506,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -2536,7 +2532,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -2562,7 +2558,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -2588,7 +2584,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -2614,7 +2610,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -2640,7 +2636,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -2666,7 +2662,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -2692,7 +2688,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -2718,7 +2714,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -2744,7 +2740,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -2770,7 +2766,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -2796,7 +2792,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -2822,7 +2818,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -2848,7 +2844,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>19</v>
       </c>
@@ -2874,7 +2870,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>27</v>
       </c>
